--- a/data/trans_bre/P6907S1-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P6907S1-Edad-trans_bre.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 20,97</t>
+          <t>-3,63; 24,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,11; 0,0</t>
+          <t>-30,72; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,51</t>
+          <t>0,0; 57,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 10,3</t>
+          <t>-12,6; 9,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,62; 6,19</t>
+          <t>-13,99; 5,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 10,19</t>
+          <t>-5,92; 10,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 16,02</t>
+          <t>-11,74; 14,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,92; 97,36</t>
+          <t>-60,91; 89,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 2156,0</t>
+          <t>-100,0; 1147,47</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 11,5</t>
+          <t>-5,58; 10,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 4,2</t>
+          <t>-17,93; 4,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 1,73</t>
+          <t>-6,31; 1,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 3,16</t>
+          <t>-15,93; 2,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-59,18; 308,44</t>
+          <t>-65,55; 273,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-72,52; 42,51</t>
+          <t>-75,5; 31,73</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 18,1</t>
+          <t>-6,88; 18,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 4,37</t>
+          <t>-7,25; 3,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 2,37</t>
+          <t>-11,21; 2,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,29; 443,12</t>
+          <t>-76,1; 386,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-77,85; 54,63</t>
+          <t>-79,55; 54,08</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 25,79</t>
+          <t>-12,21; 22,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,59; 0,0</t>
+          <t>-25,72; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,78</t>
+          <t>0,0; 17,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 6,31</t>
+          <t>-14,49; 5,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-72,2; 70,8</t>
+          <t>-69,62; 77,72</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 6,84</t>
+          <t>-3,18; 6,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 2,17</t>
+          <t>-7,54; 2,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 2,08</t>
+          <t>-3,84; 2,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 1,68</t>
+          <t>-7,3; 2,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,04; 88,33</t>
+          <t>-29,84; 92,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 96,97</t>
+          <t>-100,0; 124,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-79,45; 108,62</t>
+          <t>-80,6; 119,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-55,55; 21,33</t>
+          <t>-54,59; 24,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6907S1-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P6907S1-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,52</t>
+          <t>14,92</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 24,11</t>
+          <t>-3,63; 19,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,72; 0,0</t>
+          <t>-30,2; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,39</t>
+          <t>0,0; 56,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,74</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 9,61</t>
+          <t>-11,16; 8,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 5,56</t>
+          <t>-14,0; 6,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 10,92</t>
+          <t>-6,38; 11,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 14,96</t>
+          <t>-16,74; 13,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,91; 89,58</t>
+          <t>-58,7; 81,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1147,47</t>
+          <t>-88,15; 630,18</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-5,42</t>
+          <t>-3,44</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-37,34%</t>
+          <t>-27,42%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 10,63</t>
+          <t>-4,84; 10,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 4,37</t>
+          <t>-17,55; 3,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 1,62</t>
+          <t>-6,78; 1,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 2,34</t>
+          <t>-12,33; 4,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-65,55; 273,28</t>
+          <t>-60,49; 259,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-75,5; 31,73</t>
+          <t>-69,21; 58,82</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,16</t>
+          <t>-0,19</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-37,54%</t>
+          <t>-2,54%</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 18,39</t>
+          <t>-5,98; 17,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 3,81</t>
+          <t>-7,26; 3,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 2,58</t>
+          <t>-6,96; 5,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,1; 386,53</t>
+          <t>-68,17; 421,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-79,55; 54,08</t>
+          <t>-60,95; 147,86</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,91</t>
+          <t>-2,59</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-28,54%</t>
+          <t>-20,18%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 22,87</t>
+          <t>-12,15; 26,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,72; 0,0</t>
+          <t>-27,9; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,25</t>
+          <t>0,0; 18,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 5,02</t>
+          <t>-11,81; 7,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-69,62; 77,72</t>
+          <t>-63,88; 95,77</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-2,69</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-24,84%</t>
+          <t>-10,17%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 6,98</t>
+          <t>-3,3; 6,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 2,45</t>
+          <t>-7,32; 2,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 2,32</t>
+          <t>-3,64; 2,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 2,18</t>
+          <t>-5,85; 3,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,84; 92,78</t>
+          <t>-30,46; 93,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 124,13</t>
+          <t>-100,0; 136,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-80,6; 119,34</t>
+          <t>-81,34; 125,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-54,59; 24,96</t>
+          <t>-43,39; 44,49</t>
         </is>
       </c>
     </row>
